--- a/master/result/33_艺术之梦_从零到传奇/33_艺术之梦_从零到传奇.xlsx
+++ b/master/result/33_艺术之梦_从零到传奇/33_艺术之梦_从零到传奇.xlsx
@@ -397,577 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>basement</v>
       </c>
       <c r="B2" t="str">
-        <v>basement</v>
+        <v>/ˈbeɪsmənt/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>地下室</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>smoke</v>
       </c>
       <c r="B3" t="str">
-        <v>smoke</v>
+        <v>/sməʊk/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>烟</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>chimney</v>
       </c>
       <c r="B4" t="str">
-        <v>chimney</v>
+        <v>/ˈtʃɪmni/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>烟囱</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>dusk</v>
       </c>
       <c r="B5" t="str">
-        <v>dusk</v>
+        <v>/dusk/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>黄昏</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>formation</v>
       </c>
       <c r="B6" t="str">
-        <v>formation</v>
+        <v>/formation/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>形式</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>kindergarten</v>
       </c>
       <c r="B7" t="str">
-        <v>kindergarten</v>
+        <v>/kindergarten/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>幼儿园</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>uniform</v>
       </c>
       <c r="B8" t="str">
-        <v>uniform</v>
+        <v>/uniform/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>制服</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>brush</v>
       </c>
       <c r="B9" t="str">
-        <v>brush</v>
+        <v>/brʌʃ/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>画笔</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>ink</v>
       </c>
       <c r="B10" t="str">
-        <v>ink</v>
+        <v>/ink/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>墨水</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>squirrel</v>
       </c>
       <c r="B11" t="str">
-        <v>squirrel</v>
+        <v>/squirrel/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>松鼠</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>crude</v>
       </c>
       <c r="B12" t="str">
-        <v>crude</v>
+        <v>/crude/</v>
       </c>
       <c r="C12" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>粗糙的</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>hill</v>
       </c>
       <c r="B13" t="str">
-        <v>hill</v>
+        <v>/hill/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>小山</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>purple</v>
       </c>
       <c r="B14" t="str">
-        <v>purple</v>
+        <v>/purple/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>紫色</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>fair</v>
       </c>
       <c r="B15" t="str">
+        <v>/fair/</v>
+      </c>
+      <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
+        <v>集市</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>gigantic</v>
+      </c>
+      <c r="B16" t="str">
+        <v>/gigantic/</v>
+      </c>
+      <c r="C16" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D16" t="str">
+        <v>巨大的</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>charm</v>
+      </c>
+      <c r="B17" t="str">
+        <v>/charm/</v>
+      </c>
+      <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
+        <v>魅力</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>recommend</v>
+      </c>
+      <c r="B18" t="str">
+        <v>/ˌrekəˈmend/</v>
+      </c>
+      <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
+        <v>推荐</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>community</v>
+      </c>
+      <c r="B19" t="str">
+        <v>/community/</v>
+      </c>
+      <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
+        <v>社区</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>wagon</v>
+      </c>
+      <c r="B20" t="str">
+        <v>/wagon/</v>
+      </c>
+      <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
+        <v>运货马车</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>exotic</v>
+      </c>
+      <c r="B21" t="str">
+        <v>/exotic/</v>
+      </c>
+      <c r="C21" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D21" t="str">
+        <v>异国情调的</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>tongue</v>
+      </c>
+      <c r="B22" t="str">
+        <v>/tongue/</v>
+      </c>
+      <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
+        <v>语言</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>laptop</v>
+      </c>
+      <c r="B23" t="str">
+        <v>/laptop/</v>
+      </c>
+      <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
+        <v>笔记本电脑</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>epoch</v>
+      </c>
+      <c r="B24" t="str">
+        <v>/epoch/</v>
+      </c>
+      <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
+        <v>时代</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>victory</v>
+      </c>
+      <c r="B25" t="str">
+        <v>/victory/</v>
+      </c>
+      <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
+        <v>胜利</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>attend</v>
+      </c>
+      <c r="B26" t="str">
+        <v>/attend/</v>
+      </c>
+      <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
+        <v>出席</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>another</v>
+      </c>
+      <c r="B27" t="str">
+        <v>/əˈnʌðə/</v>
+      </c>
+      <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
+        <v>另一个</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>heroic</v>
+      </c>
+      <c r="B28" t="str">
+        <v>/heroic/</v>
+      </c>
+      <c r="C28" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>英勇的</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>religion</v>
+      </c>
+      <c r="B29" t="str">
+        <v>/religion/</v>
+      </c>
+      <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
+        <v>宗教</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>consult</v>
+      </c>
+      <c r="B30" t="str">
+        <v>/consult/</v>
+      </c>
+      <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
+        <v>咨询</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>launch</v>
+      </c>
+      <c r="B31" t="str">
+        <v>/lɔːntʃ/</v>
+      </c>
+      <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
+        <v>发起</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>newspaper</v>
+      </c>
+      <c r="B32" t="str">
+        <v>/newspaper/</v>
+      </c>
+      <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
+        <v>报纸</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>latter</v>
+      </c>
+      <c r="B33" t="str">
+        <v>/latter/</v>
+      </c>
+      <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
+        <v>后者</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>ago</v>
+      </c>
+      <c r="B34" t="str">
+        <v>/ago/</v>
+      </c>
+      <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
+        <v>以前</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>beverage</v>
+      </c>
+      <c r="B35" t="str">
+        <v>/beverage/</v>
+      </c>
+      <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
+        <v>饮料</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>crystal</v>
+      </c>
+      <c r="B36" t="str">
+        <v>/ˈkrɪstəl/</v>
+      </c>
+      <c r="C36" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D36" t="str">
+        <v>水晶</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>engage</v>
+      </c>
+      <c r="B37" t="str">
+        <v>/ɪnˈɡeɪdʒ/</v>
+      </c>
+      <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
+        <v>订婚</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>platform</v>
+      </c>
+      <c r="B38" t="str">
+        <v>/platform/</v>
+      </c>
+      <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
+        <v>平台</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>donkey</v>
+      </c>
+      <c r="B39" t="str">
+        <v>/donkey/</v>
+      </c>
+      <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
+        <v>驴子</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>metal</v>
+      </c>
+      <c r="B40" t="str">
+        <v>/metal/</v>
+      </c>
+      <c r="C40" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D40" t="str">
+        <v>金属</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>simply</v>
+      </c>
+      <c r="B41" t="str">
+        <v>/simply/</v>
+      </c>
+      <c r="C41" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D41" t="str">
+        <v>仅仅</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>futile</v>
+      </c>
+      <c r="B42" t="str">
+        <v>/futile/</v>
+      </c>
+      <c r="C42" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D42" t="str">
+        <v>无效的</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>now</v>
+      </c>
+      <c r="B43" t="str">
+        <v>/now/</v>
+      </c>
+      <c r="C43" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D43" t="str">
+        <v>现在</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>forward</v>
+      </c>
+      <c r="B44" t="str">
+        <v>/forward/</v>
+      </c>
+      <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
+        <v>向前</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>perfect</v>
+      </c>
+      <c r="B45" t="str">
+        <v>/perfect/</v>
+      </c>
+      <c r="C45" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D45" t="str">
+        <v>完美的</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>dignity</v>
+      </c>
+      <c r="B46" t="str">
+        <v>/dignity/</v>
+      </c>
+      <c r="C46" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D46" t="str">
+        <v>尊严</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
         <v>fair</v>
       </c>
-      <c r="C15" t="str">
-        <v>集市</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="str">
-        <v>gigantic</v>
-      </c>
-      <c r="C16" t="str">
-        <v>巨大的</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="str">
-        <v>charm</v>
-      </c>
-      <c r="C17" t="str">
-        <v>魅力</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="str">
-        <v>recommend</v>
-      </c>
-      <c r="C18" t="str">
-        <v>推荐</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="str">
-        <v>community</v>
-      </c>
-      <c r="C19" t="str">
-        <v>社区</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="str">
-        <v>wagon</v>
-      </c>
-      <c r="C20" t="str">
-        <v>运货马车</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="str">
-        <v>exotic</v>
-      </c>
-      <c r="C21" t="str">
-        <v>异国情调的</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="str">
-        <v>tongue</v>
-      </c>
-      <c r="C22" t="str">
-        <v>语言</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="str">
-        <v>laptop</v>
-      </c>
-      <c r="C23" t="str">
-        <v>笔记本电脑</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="str">
-        <v>epoch</v>
-      </c>
-      <c r="C24" t="str">
-        <v>时代</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="str">
-        <v>victory</v>
-      </c>
-      <c r="C25" t="str">
-        <v>胜利</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="str">
-        <v>attend</v>
-      </c>
-      <c r="C26" t="str">
-        <v>出席</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="str">
-        <v>another</v>
-      </c>
-      <c r="C27" t="str">
-        <v>另一个</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="str">
-        <v>heroic</v>
-      </c>
-      <c r="C28" t="str">
-        <v>英勇的</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="str">
-        <v>religion</v>
-      </c>
-      <c r="C29" t="str">
-        <v>宗教</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="str">
-        <v>consult</v>
-      </c>
-      <c r="C30" t="str">
-        <v>咨询</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="str">
-        <v>launch</v>
-      </c>
-      <c r="C31" t="str">
-        <v>发起</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="str">
-        <v>newspaper</v>
-      </c>
-      <c r="C32" t="str">
-        <v>报纸</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="str">
-        <v>latter</v>
-      </c>
-      <c r="C33" t="str">
-        <v>后者</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="str">
-        <v>ago</v>
-      </c>
-      <c r="C34" t="str">
-        <v>以前</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="str">
-        <v>beverage</v>
-      </c>
-      <c r="C35" t="str">
-        <v>饮料</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="str">
-        <v>crystal</v>
-      </c>
-      <c r="C36" t="str">
-        <v>水晶</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="str">
-        <v>engage</v>
-      </c>
-      <c r="C37" t="str">
-        <v>订婚</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
-        <v>platform</v>
-      </c>
-      <c r="C38" t="str">
-        <v>平台</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>donkey</v>
-      </c>
-      <c r="C39" t="str">
-        <v>驴子</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>metal</v>
-      </c>
-      <c r="C40" t="str">
-        <v>金属</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>simply</v>
-      </c>
-      <c r="C41" t="str">
-        <v>仅仅</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>futile</v>
-      </c>
-      <c r="C42" t="str">
-        <v>无效的</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>now</v>
-      </c>
-      <c r="C43" t="str">
-        <v>现在</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>forward</v>
-      </c>
-      <c r="C44" t="str">
-        <v>向前</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>perfect</v>
-      </c>
-      <c r="C45" t="str">
-        <v>完美的</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>dignity</v>
-      </c>
-      <c r="C46" t="str">
-        <v>尊严</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
       <c r="B47" t="str">
-        <v>fair</v>
+        <v>/fair/</v>
       </c>
       <c r="C47" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D47" t="str">
         <v>公平的</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>haul</v>
       </c>
       <c r="B48" t="str">
-        <v>haul</v>
+        <v>/haul/</v>
       </c>
       <c r="C48" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D48" t="str">
         <v>拖运</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>cassette</v>
       </c>
       <c r="B49" t="str">
-        <v>cassette</v>
+        <v>/kəˈset/</v>
       </c>
       <c r="C49" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D49" t="str">
         <v>磁带</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>inverse</v>
       </c>
       <c r="B50" t="str">
-        <v>inverse</v>
+        <v>/inverse/</v>
       </c>
       <c r="C50" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D50" t="str">
         <v>相反的</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>frequency</v>
       </c>
       <c r="B51" t="str">
-        <v>frequency</v>
+        <v>/frequency/</v>
       </c>
       <c r="C51" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D51" t="str">
         <v>频率</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>